--- a/TechComm/assignments/informational-report/info-report-rubric/info-rpt-rubric-revised-2026-03-18.xlsx
+++ b/TechComm/assignments/informational-report/info-report-rubric/info-rpt-rubric-revised-2026-03-18.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/85df9cffced7e2ed/Documents/github/tracigardner.github.io/TechComm/assignments/informational-report/info-report-rubric/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{350AECB4-4B12-424A-80A2-1594EE206A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{350AECB4-4B12-424A-80A2-1594EE206A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8563AC61-C68F-4E83-9C00-7670ADE13999}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="255" windowWidth="27285" windowHeight="15000" xr2:uid="{6F4A49D3-23EA-444C-8FE4-1FBF3DE0966A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6F4A49D3-23EA-444C-8FE4-1FBF3DE0966A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="88">
   <si>
     <t>Letter of Transmittal</t>
   </si>
@@ -255,6 +255,51 @@
   </si>
   <si>
     <t>Does not meet three or more of the requirements.</t>
+  </si>
+  <si>
+    <t>title_or_outcome_id</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>use_range</t>
+  </si>
+  <si>
+    <t>rating_points_1</t>
+  </si>
+  <si>
+    <t>rating_title_1</t>
+  </si>
+  <si>
+    <t>rating_description_1</t>
+  </si>
+  <si>
+    <t>rating_points_2</t>
+  </si>
+  <si>
+    <t>rating_title_2</t>
+  </si>
+  <si>
+    <t>rating_description_2</t>
+  </si>
+  <si>
+    <t>rating_points_3</t>
+  </si>
+  <si>
+    <t>rating_title_3</t>
+  </si>
+  <si>
+    <t>rating_description_3</t>
+  </si>
+  <si>
+    <t>rating_points_4</t>
+  </si>
+  <si>
+    <t>rating_title_4</t>
+  </si>
+  <si>
+    <t>rating_description_4</t>
   </si>
 </sst>
 </file>
@@ -368,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -385,20 +430,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -747,22 +791,21 @@
   <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17" style="7" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="39.42578125" style="7" customWidth="1"/>
-    <col min="7" max="7" width="3.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5" style="7" customWidth="1"/>
-    <col min="14" max="14" width="17.5703125" style="7" customWidth="1"/>
-    <col min="15" max="15" width="17.7109375" style="7" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" style="7"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.42578125" customWidth="1"/>
+    <col min="7" max="7" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5" customWidth="1"/>
+    <col min="14" max="14" width="17.5703125" customWidth="1"/>
+    <col min="15" max="15" width="29.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -772,22 +815,52 @@
       <c r="A2" s="6"/>
     </row>
     <row r="3" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="11"/>
+      <c r="A3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="P3" s="10"/>
     </row>
     <row r="4" spans="1:16" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -799,43 +872,43 @@
       <c r="C4" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <v>10</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="11">
         <v>8</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="11" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="11">
         <v>6</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="11" t="s">
         <v>6</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="M4" s="12">
-        <v>0</v>
-      </c>
-      <c r="N4" s="12" t="s">
+      <c r="M4" s="11">
+        <v>0</v>
+      </c>
+      <c r="N4" s="11" t="s">
         <v>71</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="P4" s="11"/>
+      <c r="P4" s="10"/>
     </row>
     <row r="5" spans="1:16" ht="390.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
@@ -847,43 +920,43 @@
       <c r="C5" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <v>9</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>7</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="12">
         <v>5</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="M5" s="13">
-        <v>0</v>
-      </c>
-      <c r="N5" s="13" t="s">
+      <c r="M5" s="12">
+        <v>0</v>
+      </c>
+      <c r="N5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="O5" s="14" t="s">
+      <c r="O5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="11"/>
+      <c r="P5" s="10"/>
     </row>
     <row r="6" spans="1:16" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
@@ -931,7 +1004,7 @@
       <c r="O6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="P6" s="11"/>
+      <c r="P6" s="10"/>
     </row>
     <row r="7" spans="1:16" ht="129" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
@@ -979,7 +1052,7 @@
       <c r="O7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="P7" s="11"/>
+      <c r="P7" s="10"/>
     </row>
     <row r="8" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -1027,7 +1100,7 @@
       <c r="O8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="P8" s="11"/>
+      <c r="P8" s="10"/>
     </row>
     <row r="9" spans="1:16" ht="186" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
@@ -1075,7 +1148,7 @@
       <c r="O9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="P9" s="11"/>
+      <c r="P9" s="10"/>
     </row>
     <row r="10" spans="1:16" ht="157.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -1123,7 +1196,7 @@
       <c r="O10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="P10" s="11"/>
+      <c r="P10" s="10"/>
     </row>
     <row r="11" spans="1:16" ht="171.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
@@ -1171,7 +1244,7 @@
       <c r="O11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="P11" s="11"/>
+      <c r="P11" s="10"/>
     </row>
     <row r="12" spans="1:16" ht="129" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
@@ -1219,7 +1292,7 @@
       <c r="O12" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="P12" s="11"/>
+      <c r="P12" s="10"/>
     </row>
     <row r="13" spans="1:16" ht="214.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
@@ -1267,7 +1340,7 @@
       <c r="O13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="P13" s="11"/>
+      <c r="P13" s="10"/>
     </row>
     <row r="14" spans="1:16" ht="228.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
@@ -1315,7 +1388,7 @@
       <c r="O14" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="P14" s="11"/>
+      <c r="P14" s="10"/>
     </row>
     <row r="15" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
@@ -1345,10 +1418,10 @@
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="4"/>
-      <c r="P15" s="11"/>
+      <c r="P15" s="10"/>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
+      <c r="A20">
         <f>100/11</f>
         <v>9.0909090909090917</v>
       </c>
